--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M17B6_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M17B6_IN_Piura.xlsx
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>1.59</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="C11" s="21">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>16.59</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="C12" s="31">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>69.28</v>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>12.53</v>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.02</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1913,11 +1913,11 @@
       </c>
       <c r="B15" s="44">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>106.5385</v>
       </c>
       <c r="C15" s="45">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.01</v>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
@@ -1938,11 +1938,11 @@
       </c>
       <c r="B16" s="47">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>19.3699</v>
       </c>
       <c r="C16" s="48">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>18.18</v>
       </c>
       <c r="D16" s="46" t="inlineStr">
         <is>
@@ -1963,11 +1963,11 @@
       </c>
       <c r="B17" s="47">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>87.1686</v>
       </c>
       <c r="C17" s="48">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>81.82</v>
       </c>
       <c r="D17" s="46" t="inlineStr">
         <is>
@@ -2161,11 +2161,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>106.5934</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2284,6 +2284,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2699,6 +2700,7 @@
       <c r="F22" s="17" t="inlineStr"/>
       <c r="G22" s="17" t="inlineStr"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
@@ -2743,6 +2745,7 @@
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27" ht="144" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
         <is>
@@ -3197,11 +3200,11 @@
       </c>
       <c r="B19" s="33">
         <f>SUM(B10:B18)</f>
-        <v/>
+        <v>875.24</v>
       </c>
       <c r="C19" s="23">
         <f>SUM(C10:C18)</f>
-        <v/>
+        <v>99.99</v>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
@@ -3211,19 +3214,19 @@
       <c r="E19" s="17" t="inlineStr"/>
       <c r="F19" s="17">
         <f>ROUND(AVERAGE(F10:F18),2)</f>
-        <v/>
+        <v>22.85</v>
       </c>
       <c r="G19" s="22">
         <f>ROUND(AVERAGE(G10:G18),4)</f>
-        <v/>
+        <v>0.451</v>
       </c>
       <c r="H19" s="23">
         <f>ROUND(AVERAGE(H10:H18),2)</f>
-        <v/>
+        <v>29.59</v>
       </c>
       <c r="I19" s="23">
         <f>ROUND(AVERAGE(I10:I18),2)</f>
-        <v/>
+        <v>69.38</v>
       </c>
     </row>
     <row r="20" ht="48" customHeight="1">
